--- a/artfynd/A 7716-2024 artfynd.xlsx
+++ b/artfynd/A 7716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134020058</v>
       </c>
       <c r="B2" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7716-2024 artfynd.xlsx
+++ b/artfynd/A 7716-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134020058</v>
       </c>
       <c r="B2" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7716-2024 artfynd.xlsx
+++ b/artfynd/A 7716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,218 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134157933</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norra bommen, Gedings mosse, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>442034</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6168671</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Simrishamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sankt Olof</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kunde inte hitta några vid södra bommen men precis vid norra bommen fanns en</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mikael Bauer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Bauer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134162324</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107695</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221705</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ängskovall</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norra bommen, Gedings mosse, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>442034</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6168671</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Simrishamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sankt Olof</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Bauer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Bauer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
